--- a/data/trans_camb/IQ2608_R3-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IQ2608_R3-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9,45</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15,43</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-14,21</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>13,91</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>15,61</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>15,99</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9,45</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15,43</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-9,82</t>
+          <t>8,88</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,03</t>
+          <t>-4,48</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 24,5</t>
+          <t>-1,9; 20,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,88; 26,78</t>
+          <t>4,45; 26,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 33,38</t>
+          <t>-38,55; 8,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 20,79</t>
+          <t>3,89; 24,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,03; 26,85</t>
+          <t>3,84; 25,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-36,75; 11,9</t>
+          <t>-20,45; 29,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,64; 18,83</t>
+          <t>4,6; 19,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,34; 23,03</t>
+          <t>8,47; 23,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 16,53</t>
+          <t>-26,19; 11,62</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13,21%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>21,56%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-19,86%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>20,65%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>23,16%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>23,73%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13,21%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>21,56%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-13,73%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>-6,45%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,03; 41,33</t>
+          <t>-2,45; 31,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,36; 43,83</t>
+          <t>5,75; 41,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 53,27</t>
+          <t>-52,62; 11,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 31,78</t>
+          <t>5,33; 41,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,92; 41,43</t>
+          <t>5,44; 41,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-50,66; 17,53</t>
+          <t>-31,45; 45,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,99; 29,2</t>
+          <t>6,32; 30,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,39; 36,27</t>
+          <t>11,53; 36,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-23,05; 24,38</t>
+          <t>-37,18; 16,96</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19,75</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>22,53</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7,71</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>19,46</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>20,55</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,73</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19,75</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>22,53</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,52</t>
+          <t>2,26</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,27</t>
+          <t>5,49</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,41; 24,54</t>
+          <t>15,13; 24,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,68; 25,6</t>
+          <t>17,92; 27,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 11,35</t>
+          <t>-0,45; 16,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,07; 24,39</t>
+          <t>14,86; 24,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,23; 27,2</t>
+          <t>15,37; 25,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 16,18</t>
+          <t>-6,86; 11,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,29; 22,82</t>
+          <t>16,2; 23,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,11; 24,98</t>
+          <t>18,22; 24,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 12,65</t>
+          <t>-0,8; 11,33</t>
         </is>
       </c>
     </row>
@@ -946,39 +946,39 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>32,53%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>37,1%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12,71%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>32,6%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>34,42%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>32,53%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>37,1%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,04%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>32,53%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>35,74%</t>
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,1; 43,06</t>
+          <t>23,52; 41,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,68; 44,8</t>
+          <t>28,18; 46,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 19,94</t>
+          <t>-0,7; 28,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,9; 42,01</t>
+          <t>23,87; 43,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,42; 47,16</t>
+          <t>24,57; 44,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 27,75</t>
+          <t>-11,1; 20,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,15; 39,56</t>
+          <t>26,05; 40,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,23; 43,32</t>
+          <t>28,94; 41,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 21,68</t>
+          <t>-1,3; 19,24</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>18,53</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14,19</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,73</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>26,16</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>21,23</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6,83</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>18,53</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>14,19</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,29</t>
+          <t>6,18</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,31</t>
+          <t>5,14</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,46; 33,27</t>
+          <t>11,17; 26,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,36; 29,77</t>
+          <t>6,71; 22,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 19,7</t>
+          <t>-10,91; 15,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,41; 26,26</t>
+          <t>17,56; 33,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,82; 21,91</t>
+          <t>12,61; 29,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,47; 15,7</t>
+          <t>-7,35; 19,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,24; 27,52</t>
+          <t>17,2; 27,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,52; 23,38</t>
+          <t>12,25; 23,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 14,68</t>
+          <t>-5,64; 14,33</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>27,38%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20,97%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5,51%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>44,25%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>35,91%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>11,56%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>27,38%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>20,97%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28,06; 63,11</t>
+          <t>15,23; 41,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22,71; 55,88</t>
+          <t>9,44; 35,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 35,8</t>
+          <t>-16,02; 24,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,33; 41,77</t>
+          <t>27,68; 63,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,46; 34,8</t>
+          <t>19,59; 55,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,02; 23,81</t>
+          <t>-11,73; 35,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,84; 46,59</t>
+          <t>25,26; 46,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,94; 39,54</t>
+          <t>18,38; 38,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 24,17</t>
+          <t>-8,45; 23,7</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>18,3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>19,73</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4,86</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>20,28</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>19,93</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4,56</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>18,3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>19,73</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,58</t>
+          <t>3,28</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,31</t>
+          <t>4,3</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,85; 23,97</t>
+          <t>14,61; 22,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,31; 24,11</t>
+          <t>15,83; 23,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 11,7</t>
+          <t>-2,59; 11,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,55; 22,17</t>
+          <t>16,15; 23,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,2; 23,08</t>
+          <t>15,95; 23,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 12,46</t>
+          <t>-3,81; 10,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,74; 22,21</t>
+          <t>16,37; 21,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,13; 22,39</t>
+          <t>17,42; 22,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 10,83</t>
+          <t>-1,36; 9,12</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>28,82%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>31,06%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7,65%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>33,48%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>32,89%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>7,53%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>28,82%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>31,06%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>25,38; 41,84</t>
+          <t>22,26; 36,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>25,82; 41,67</t>
+          <t>23,87; 37,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 19,49</t>
+          <t>-3,89; 17,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22,07; 36,45</t>
+          <t>25,8; 40,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,34; 37,59</t>
+          <t>25,25; 40,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 20,01</t>
+          <t>-6,19; 17,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,32; 36,8</t>
+          <t>25,5; 36,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>27,0; 37,21</t>
+          <t>27,41; 37,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,71; 17,4</t>
+          <t>-2,22; 15,02</t>
         </is>
       </c>
     </row>
